--- a/artfynd/A 65198-2023 artfynd.xlsx
+++ b/artfynd/A 65198-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65198-2023 artfynd.xlsx
+++ b/artfynd/A 65198-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,6 +917,128 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114942602</v>
+      </c>
+      <c r="B4" t="n">
+        <v>76920</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1095</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mussellav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Normandina pulchella</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Borrer) Nyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Klevatorpet, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>338446</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6358270</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Frillesås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65198-2023 artfynd.xlsx
+++ b/artfynd/A 65198-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6985731</v>
+        <v>114942602</v>
       </c>
       <c r="B2" t="n">
-        <v>93146</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2666</v>
+        <v>1095</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Mussellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neckera crispa</t>
+          <t>Normandina pulchella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Borrer) Nyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Glamsjö, VSV om, Hl</t>
+          <t>Klevatorpet, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338534.8018782604</v>
+        <v>338446</v>
       </c>
       <c r="R2" t="n">
-        <v>6358335.249219909</v>
+        <v>6358271</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-09-30</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-09-30</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,25 +777,15 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Bokskog gränsande till askskog i sluttning</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Sten</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kjell Georgson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kjell Georgson, Jesper Lind</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -800,12 +795,7 @@
         <v>6985723</v>
       </c>
       <c r="B3" t="n">
-        <v>95220</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338534.8018782604</v>
+        <v>338535</v>
       </c>
       <c r="R3" t="n">
-        <v>6358335.249219909</v>
+        <v>6358335</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -870,19 +860,9 @@
           <t>2013-09-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114942602</v>
+        <v>6985731</v>
       </c>
       <c r="B4" t="n">
-        <v>76971</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,47 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1095</v>
+        <v>2666</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mussellav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Normandina pulchella</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Borrer) Nyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Klevatorpet, Hl</t>
+          <t>Glamsjö, VSV om, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338446</v>
+        <v>338535</v>
       </c>
       <c r="R4" t="n">
-        <v>6358271</v>
+        <v>6358335</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2013-09-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2013-09-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +981,25 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bokskog gränsande till askskog i sluttning</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sten</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sindy Gullberg</t>
+          <t>Kjell Georgson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sindy Gullberg</t>
+          <t>Kjell Georgson, Jesper Lind</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 65198-2023 artfynd.xlsx
+++ b/artfynd/A 65198-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114942602</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6985723</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,8 +1018,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6985731</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>